--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-12 05:23:30</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-13 05:38:53</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>340.10</t>
+          <t>340.1</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>336.60</t>
+          <t>336.6</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>333.40</t>
+          <t>333.4</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -2496,9 +2496,9 @@
           <t>11817</t>
         </is>
       </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>-2.06%</t>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3213,32 +3213,32 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>313.65</t>
+          <t>284.25</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>314.50</t>
+          <t>289.00</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>314.50</t>
+          <t>291.50</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>313.50</t>
+          <t>283.85</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14448</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>-9.85%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-13 05:38:53</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-14 05:46:15</t>
         </is>
       </c>
     </row>
@@ -2473,12 +2473,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>333.10</t>
+          <t>333.1</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>338.00</t>
+          <t>338.0</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>331.00</t>
+          <t>331.0</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>+1.50%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3213,32 +3213,32 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>284.25</t>
+          <t>313.65</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>289.00</t>
+          <t>314.50</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>291.50</t>
+          <t>314.50</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>283.85</t>
+          <t>313.50</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>14448</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>-9.85%</t>
+          <t>-0.52%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$100</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-14 05:46:15</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-15 05:47:29</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>338.10</t>
+          <t>338.1</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>340.70</t>
+          <t>340.7</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>+2.07%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
@@ -3245,698 +3245,698 @@
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>307.35</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>308.50</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>308.50</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>305.00</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-2.01%</t>
         </is>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G85" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G87" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
@@ -3948,116 +3948,153 @@
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="22" customHeight="1">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="B100" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr">
+      <c r="C100" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D99" s="4" t="inlineStr">
+      <c r="D100" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
+      <c r="E100" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F99" s="4" t="inlineStr">
+      <c r="F100" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G99" s="6" t="inlineStr">
+      <c r="G100" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G99"/>
+  <autoFilter ref="A4:G100"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-15 05:47:29</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-16 05:37:12</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>49</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
@@ -3282,698 +3282,698 @@
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>299.65</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>299.65</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>299.65</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>299.65</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>49</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-2.51%</t>
         </is>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G83" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G84" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G85" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G86" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G93" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
@@ -3985,116 +3985,153 @@
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="22" customHeight="1">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B100" s="4" t="inlineStr">
+      <c r="B101" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C100" s="4" t="inlineStr">
+      <c r="C101" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D100" s="4" t="inlineStr">
+      <c r="D101" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
+      <c r="E101" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F100" s="4" t="inlineStr">
+      <c r="F101" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G100" s="6" t="inlineStr">
+      <c r="G101" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G100"/>
+  <autoFilter ref="A4:G101"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$102</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-16 05:37:12</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-17 05:42:48</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
@@ -3319,698 +3319,698 @@
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>295.85</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>295.85</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>295.85</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>295.85</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-1.27%</t>
         </is>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G85" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G87" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr">
@@ -4022,116 +4022,153 @@
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="22" customHeight="1">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B101" s="4" t="inlineStr">
+      <c r="B102" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C101" s="4" t="inlineStr">
+      <c r="C102" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D101" s="4" t="inlineStr">
+      <c r="D102" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
+      <c r="E102" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F101" s="4" t="inlineStr">
+      <c r="F102" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G101" s="6" t="inlineStr">
+      <c r="G102" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G101"/>
+  <autoFilter ref="A4:G102"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-17 05:42:48</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-18 05:32:22</t>
         </is>
       </c>
     </row>
@@ -2547,22 +2547,22 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>345.10</t>
+          <t>345.1</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>338.50</t>
+          <t>338.5</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>354.00</t>
+          <t>354.0</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>338.50</t>
+          <t>338.5</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>+5.30%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
@@ -3356,698 +3356,698 @@
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>290.55</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>290.55</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>290.55</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>290.55</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-1.79%</t>
         </is>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G84" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G85" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G86" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G89" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G95" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
@@ -4059,116 +4059,153 @@
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="22" customHeight="1">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B102" s="4" t="inlineStr">
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C102" s="4" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D102" s="4" t="inlineStr">
+      <c r="D103" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
+      <c r="E103" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F102" s="4" t="inlineStr">
+      <c r="F103" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G102" s="6" t="inlineStr">
+      <c r="G103" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G102"/>
+  <autoFilter ref="A4:G103"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$104</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-18 05:32:22</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-19 05:28:51</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>363.40</t>
+          <t>363.4</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>344.90</t>
+          <t>344.9</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -2644,9 +2644,9 @@
           <t>5463</t>
         </is>
       </c>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t>-1.07%</t>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3393,698 +3393,698 @@
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>294.55</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>294.55</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>294.55</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>294.55</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>+1.38%</t>
         </is>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G85" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G87" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
@@ -4096,116 +4096,153 @@
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="22" customHeight="1">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B103" s="4" t="inlineStr">
+      <c r="B104" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C103" s="4" t="inlineStr">
+      <c r="C104" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D103" s="4" t="inlineStr">
+      <c r="D104" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
+      <c r="E104" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F103" s="4" t="inlineStr">
+      <c r="F104" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G103" s="6" t="inlineStr">
+      <c r="G104" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G103"/>
+  <autoFilter ref="A4:G104"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-19 05:28:51</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-20 05:41:40</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>359.50</t>
+          <t>359.5</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>369.20</t>
+          <t>369.2</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>355.00</t>
+          <t>355.0</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3398,32 +3398,32 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>294.55</t>
+          <t>277.20</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>294.55</t>
+          <t>279.00</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>294.55</t>
+          <t>281.00</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>294.55</t>
+          <t>275.05</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t>+1.38%</t>
+          <t>11205</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>-4.59%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-20 05:41:40</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-21 05:53:33</t>
         </is>
       </c>
     </row>
@@ -2658,22 +2658,22 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>363.60</t>
+          <t>363.6</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>359.80</t>
+          <t>359.8</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>366.10</t>
+          <t>366.1</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>351.20</t>
+          <t>351.2</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -2718,9 +2718,9 @@
           <t>301</t>
         </is>
       </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>-1.33%</t>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3398,32 +3398,32 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>277.20</t>
+          <t>294.55</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>279.00</t>
+          <t>294.55</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>281.00</t>
+          <t>294.55</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>275.05</t>
+          <t>294.55</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>11205</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>-4.59%</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>+1.38%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$105</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-21 05:53:33</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-22 05:50:47</t>
         </is>
       </c>
     </row>
@@ -2705,12 +2705,12 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>370.10</t>
+          <t>370.1</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>359.00</t>
+          <t>359.0</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>+5.30%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11205</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -3430,698 +3430,698 @@
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>276.40</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>279.70</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>283.50</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>11205</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-6.16%</t>
         </is>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G86" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G89" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G91" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G92" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G97" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
@@ -4133,116 +4133,153 @@
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="22" customHeight="1">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B104" s="4" t="inlineStr">
+      <c r="B105" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C104" s="4" t="inlineStr">
+      <c r="C105" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D104" s="4" t="inlineStr">
+      <c r="D105" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E104" s="4" t="inlineStr">
+      <c r="E105" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F104" s="4" t="inlineStr">
+      <c r="F105" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G104" s="6" t="inlineStr">
+      <c r="G105" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G104"/>
+  <autoFilter ref="A4:G105"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$106</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-22 05:50:47</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-23 05:28:46</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>11205</t>
+          <t>13363</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
@@ -3467,698 +3467,698 @@
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>272.30</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>275.00</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>278.50</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>271.30</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>13363</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-1.48%</t>
         </is>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G87" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
@@ -4170,116 +4170,153 @@
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="22" customHeight="1">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B105" s="4" t="inlineStr">
+      <c r="B106" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C105" s="4" t="inlineStr">
+      <c r="C106" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D105" s="4" t="inlineStr">
+      <c r="D106" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E105" s="4" t="inlineStr">
+      <c r="E106" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F105" s="4" t="inlineStr">
+      <c r="F106" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G105" s="6" t="inlineStr">
+      <c r="G106" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G105"/>
+  <autoFilter ref="A4:G106"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$107</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-23 05:28:46</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-24 05:50:32</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>13363</t>
+          <t>15733</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
@@ -3504,698 +3504,698 @@
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>275.90</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>272.10</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>278.95</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>269.75</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G85" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>15733</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>+1.32%</t>
         </is>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G89" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G91" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G92" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G93" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G99" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G103" s="6" t="inlineStr">
@@ -4207,116 +4207,153 @@
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="22" customHeight="1">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B106" s="4" t="inlineStr">
+      <c r="B107" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C106" s="4" t="inlineStr">
+      <c r="C107" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D106" s="4" t="inlineStr">
+      <c r="D107" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E106" s="4" t="inlineStr">
+      <c r="E107" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F106" s="4" t="inlineStr">
+      <c r="F107" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G106" s="6" t="inlineStr">
+      <c r="G107" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G106"/>
+  <autoFilter ref="A4:G107"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$108</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-24 05:50:32</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-25 05:47:00</t>
         </is>
       </c>
     </row>
@@ -2792,9 +2792,9 @@
           <t>49</t>
         </is>
       </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>-1.68%</t>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>15733</t>
+          <t>14984</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -3541,698 +3541,698 @@
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>275.35</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>275.05</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>279.10</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>272.00</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>14984</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-0.20%</t>
         </is>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
@@ -4244,116 +4244,153 @@
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="22" customHeight="1">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B107" s="4" t="inlineStr">
+      <c r="B108" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C107" s="4" t="inlineStr">
+      <c r="C108" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D107" s="4" t="inlineStr">
+      <c r="D108" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E107" s="4" t="inlineStr">
+      <c r="E108" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F107" s="4" t="inlineStr">
+      <c r="F108" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G107" s="6" t="inlineStr">
+      <c r="G108" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G107"/>
+  <autoFilter ref="A4:G108"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$109</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-25 05:47:00</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-26 05:50:07</t>
         </is>
       </c>
     </row>
@@ -2769,22 +2769,22 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>371.40</t>
+          <t>371.4</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>376.70</t>
+          <t>376.7</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>377.00</t>
+          <t>377.0</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>366.50</t>
+          <t>366.5</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -2829,9 +2829,9 @@
           <t>60</t>
         </is>
       </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>-3.72%</t>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>14984</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
@@ -3578,698 +3578,698 @@
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>278.60</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>274.30</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>284.30</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>9519</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>+1.18%</t>
         </is>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G91" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G92" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G93" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G95" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G96" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G101" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
@@ -4281,116 +4281,153 @@
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="22" customHeight="1">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B108" s="4" t="inlineStr">
+      <c r="B109" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C108" s="4" t="inlineStr">
+      <c r="C109" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D108" s="4" t="inlineStr">
+      <c r="D109" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E108" s="4" t="inlineStr">
+      <c r="E109" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F108" s="4" t="inlineStr">
+      <c r="F109" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G108" s="6" t="inlineStr">
+      <c r="G109" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G108"/>
+  <autoFilter ref="A4:G109"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-26 05:50:07</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-27 06:11:32</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>357.60</t>
+          <t>357.6</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -2866,9 +2866,9 @@
           <t>39</t>
         </is>
       </c>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t>-4.39%</t>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>278.60</t>
+          <t>278.10</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>9519</t>
+          <t>12465</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>+1.18%</t>
+          <t>+1.00%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-27 06:11:32</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-28 06:18:14</t>
         </is>
       </c>
     </row>
@@ -2843,22 +2843,22 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>341.90</t>
+          <t>341.9</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>355.40</t>
+          <t>355.4</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>355.40</t>
+          <t>355.4</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>342.90</t>
+          <t>342.9</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>+1.16%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>278.10</t>
+          <t>278.60</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>12465</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>+1.18%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$110</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-28 06:18:14</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-29 06:33:56</t>
         </is>
       </c>
     </row>
@@ -2940,9 +2940,9 @@
           <t>8</t>
         </is>
       </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>-0.56%</t>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>9519</t>
+          <t>12465</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
@@ -3615,698 +3615,698 @@
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>288.75</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>277.90</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>291.50</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>277.05</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>12465</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>+3.64%</t>
         </is>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G97" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
@@ -4318,116 +4318,153 @@
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="22" customHeight="1">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B109" s="4" t="inlineStr">
+      <c r="B110" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C109" s="4" t="inlineStr">
+      <c r="C110" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D109" s="4" t="inlineStr">
+      <c r="D110" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
+      <c r="E110" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F109" s="4" t="inlineStr">
+      <c r="F110" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G109" s="6" t="inlineStr">
+      <c r="G110" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G109"/>
+  <autoFilter ref="A4:G110"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$111</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-29 06:33:56</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-30 06:16:54</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>12465</t>
+          <t>18321</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -3652,698 +3652,698 @@
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>289.45</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>289.00</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>293.40</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>281.80</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G89" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>18321</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>+0.24%</t>
         </is>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G92" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G93" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G95" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G96" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G97" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G98" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G103" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
@@ -4355,116 +4355,153 @@
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="22" customHeight="1">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B110" s="4" t="inlineStr">
+      <c r="B111" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C110" s="4" t="inlineStr">
+      <c r="C111" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D110" s="4" t="inlineStr">
+      <c r="D111" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
+      <c r="E111" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F110" s="4" t="inlineStr">
+      <c r="F111" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G110" s="6" t="inlineStr">
+      <c r="G111" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G110"/>
+  <autoFilter ref="A4:G111"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$112</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-09-30 06:16:54</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-01 06:48:37</t>
         </is>
       </c>
     </row>
@@ -2917,12 +2917,12 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>343.90</t>
+          <t>343.9</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>343.60</t>
+          <t>343.6</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>343.00</t>
+          <t>343.0</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -2977,9 +2977,9 @@
           <t>8</t>
         </is>
       </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t>-0.48%</t>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>18321</t>
+          <t>15002</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
@@ -3689,698 +3689,698 @@
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>290.70</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>292.00</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>298.80</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>289.05</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>15002</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>+0.43%</t>
         </is>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G97" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G99" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G104" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
@@ -4392,116 +4392,153 @@
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="22" customHeight="1">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B111" s="4" t="inlineStr">
+      <c r="B112" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C111" s="4" t="inlineStr">
+      <c r="C112" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D111" s="4" t="inlineStr">
+      <c r="D112" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
+      <c r="E112" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F111" s="4" t="inlineStr">
+      <c r="F112" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G111" s="6" t="inlineStr">
+      <c r="G112" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G111"/>
+  <autoFilter ref="A4:G112"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$113</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-01 06:48:37</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-02 06:40:00</t>
         </is>
       </c>
     </row>
@@ -2959,17 +2959,17 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>345.00</t>
+          <t>345.0</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>345.00</t>
+          <t>345.0</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>333.00</t>
+          <t>333.0</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -3014,9 +3014,9 @@
           <t>18</t>
         </is>
       </c>
-      <c r="G71" s="6" t="inlineStr">
-        <is>
-          <t>-4.05%</t>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>15002</t>
+          <t>14153</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
@@ -3726,698 +3726,698 @@
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>288.25</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>288.50</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>290.90</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>283.30</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>14153</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-0.84%</t>
         </is>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G95" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G96" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G97" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G98" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G99" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G100" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G105" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
@@ -4429,116 +4429,153 @@
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="22" customHeight="1">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B112" s="4" t="inlineStr">
+      <c r="B113" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C112" s="4" t="inlineStr">
+      <c r="C113" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D112" s="4" t="inlineStr">
+      <c r="D113" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
+      <c r="E113" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F112" s="4" t="inlineStr">
+      <c r="F113" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G112" s="6" t="inlineStr">
+      <c r="G113" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G112"/>
+  <autoFilter ref="A4:G113"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$114</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-02 06:40:00</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-03 06:01:06</t>
         </is>
       </c>
     </row>
@@ -2991,22 +2991,22 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>328.40</t>
+          <t>328.4</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>333.00</t>
+          <t>333.0</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>334.00</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>328.00</t>
+          <t>328.0</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -3051,9 +3051,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="G72" s="6" t="inlineStr">
-        <is>
-          <t>-1.23%</t>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>14153</t>
+          <t>13368</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
@@ -3763,698 +3763,698 @@
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>288.75</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>290.50</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>298.55</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>288.10</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>13368</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>+0.17%</t>
         </is>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G97" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G99" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G101" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
@@ -4466,116 +4466,153 @@
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="22" customHeight="1">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B113" s="4" t="inlineStr">
+      <c r="B114" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C113" s="4" t="inlineStr">
+      <c r="C114" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D113" s="4" t="inlineStr">
+      <c r="D114" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
+      <c r="E114" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F113" s="4" t="inlineStr">
+      <c r="F114" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G113" s="6" t="inlineStr">
+      <c r="G114" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G113"/>
+  <autoFilter ref="A4:G114"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-03 06:01:06</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-04 06:37:47</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>325.50</t>
+          <t>325.5</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>320.00</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -3088,9 +3088,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>-0.03%</t>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>288.75</t>
+          <t>290.75</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -3788,12 +3788,12 @@
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>13368</t>
+          <t>13126</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+0.87%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-04 06:37:47</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-05 06:32:17</t>
         </is>
       </c>
     </row>
@@ -3125,9 +3125,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>-1.79%</t>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>290.75</t>
+          <t>288.75</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -3788,12 +3788,12 @@
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>13368</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>+0.87%</t>
+          <t>+0.17%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$115</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-05 06:32:17</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-06 07:10:06</t>
         </is>
       </c>
     </row>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>13368</t>
+          <t>13126</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -3800,698 +3800,698 @@
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>292.55</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>293.15</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>299.60</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>291.30</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G93" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>13126</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>+1.32%</t>
         </is>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G96" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G97" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G98" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G99" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G100" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G101" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G102" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G107" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
@@ -4503,116 +4503,153 @@
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="22" customHeight="1">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B114" s="4" t="inlineStr">
+      <c r="B115" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C114" s="4" t="inlineStr">
+      <c r="C115" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D114" s="4" t="inlineStr">
+      <c r="D115" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
+      <c r="E115" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F114" s="4" t="inlineStr">
+      <c r="F115" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G114" s="6" t="inlineStr">
+      <c r="G115" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G114"/>
+  <autoFilter ref="A4:G115"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$116</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-06 07:10:06</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-07 06:49:56</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>18321</t>
+          <t>12465</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>15448</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
@@ -3837,698 +3837,698 @@
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>304.45</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>293.10</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>306.45</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>291.50</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>15448</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>+4.07%</t>
         </is>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G97" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G99" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G101" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G103" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
@@ -4540,116 +4540,153 @@
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="22" customHeight="1">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B115" s="4" t="inlineStr">
+      <c r="B116" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C115" s="4" t="inlineStr">
+      <c r="C116" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D115" s="4" t="inlineStr">
+      <c r="D116" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
+      <c r="E116" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F115" s="4" t="inlineStr">
+      <c r="F116" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G115" s="6" t="inlineStr">
+      <c r="G116" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G115"/>
+  <autoFilter ref="A4:G116"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-07 06:49:56</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-08 06:58:58</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$118</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-08 06:58:58</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-09 07:07:16</t>
         </is>
       </c>
     </row>
@@ -3107,17 +3107,17 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>313.80</t>
+          <t>313.8</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>313.80</t>
+          <t>313.8</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>313.80</t>
+          <t>313.8</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>12465</t>
+          <t>18321</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>15448</t>
+          <t>20967</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -3874,234 +3874,234 @@
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>292.70</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>302.90</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>308.35</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>292.05</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>18777</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-3.86%</t>
         </is>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>289.05</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>293.90</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>294.90</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>286.00</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>18777</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-1.25%</t>
         </is>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G98" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>15.13K</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
+          <t>13.83K</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
+          <t>12.68K</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -4111,582 +4111,656 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
+          <t>8.18K</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
+          <t>11.87K</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>+1.63%</t>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
+          <t>10.80K</t>
         </is>
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>-3.15%</t>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
+          <t>13.92K</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
-        </is>
-      </c>
-      <c r="G105" s="5" t="inlineStr">
-        <is>
-          <t>+2.31%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G109" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>23.18K</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
-        </is>
-      </c>
-      <c r="G110" s="6" t="inlineStr">
-        <is>
-          <t>-1.88%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G115" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="4" t="inlineStr">
         <is>
+          <t>2026年6月5日</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>246.5</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>248.0</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>249.2</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>243.3</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>26.62K</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>-0.26%</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="22" customHeight="1">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G117" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="22" customHeight="1">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B116" s="4" t="inlineStr">
+      <c r="B118" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C116" s="4" t="inlineStr">
+      <c r="C118" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D116" s="4" t="inlineStr">
+      <c r="D118" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
+      <c r="E118" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F116" s="4" t="inlineStr">
+      <c r="F118" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G116" s="6" t="inlineStr">
+      <c r="G118" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G116"/>
+  <autoFilter ref="A4:G118"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$119</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-09 07:07:16</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-10 06:40:13</t>
         </is>
       </c>
     </row>
@@ -3139,22 +3139,22 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>319.20</t>
+          <t>319.2</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>319.20</t>
+          <t>319.2</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>319.20</t>
+          <t>319.2</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>319.20</t>
+          <t>319.2</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -3199,9 +3199,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G76" s="6" t="inlineStr">
-        <is>
-          <t>-1.22%</t>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>18321</t>
+          <t>12465</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>20967</t>
+          <t>15448</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>18777</t>
+          <t>14516</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
@@ -3948,698 +3948,698 @@
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>286.95</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>289.05</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>291.80</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>284.25</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>14516</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-0.73%</t>
         </is>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G100" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G101" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G102" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G103" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G104" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G105" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G106" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G111" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G115" s="6" t="inlineStr">
@@ -4651,116 +4651,153 @@
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="22" customHeight="1">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B118" s="4" t="inlineStr">
+      <c r="B119" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C118" s="4" t="inlineStr">
+      <c r="C119" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D118" s="4" t="inlineStr">
+      <c r="D119" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
+      <c r="E119" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F118" s="4" t="inlineStr">
+      <c r="F119" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G118" s="6" t="inlineStr">
+      <c r="G119" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G118"/>
+  <autoFilter ref="A4:G119"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-10 06:40:13</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-11 06:47:20</t>
         </is>
       </c>
     </row>
@@ -3176,22 +3176,22 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>315.30</t>
+          <t>315.3</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>315.30</t>
+          <t>315.3</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>315.30</t>
+          <t>315.3</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>315.30</t>
+          <t>315.3</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -3236,9 +3236,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="G77" s="6" t="inlineStr">
-        <is>
-          <t>-0.52%</t>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>286.95</t>
+          <t>285.15</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -3968,17 +3968,17 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>284.25</t>
+          <t>284.30</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>14516</t>
+          <t>14830</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>-1.35%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-11 06:47:20</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-12 06:57:06</t>
         </is>
       </c>
     </row>
@@ -3218,17 +3218,17 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>314.50</t>
+          <t>314.5</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>314.50</t>
+          <t>314.5</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>313.50</t>
+          <t>313.5</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -3273,9 +3273,9 @@
           <t>49</t>
         </is>
       </c>
-      <c r="G78" s="6" t="inlineStr">
-        <is>
-          <t>-2.01%</t>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>285.15</t>
+          <t>286.95</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -3968,17 +3968,17 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>284.30</t>
+          <t>284.25</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>14830</t>
+          <t>14516</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>-1.35%</t>
+          <t>-0.73%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$120</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-12 06:57:06</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-13 07:20:28</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>14516</t>
+          <t>14830</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
@@ -3985,698 +3985,698 @@
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>290.60</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>287.50</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>290.95</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>283.50</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>14830</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>+1.27%</t>
         </is>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G101" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G103" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G104" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G105" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G107" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G112" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G115" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
@@ -4688,116 +4688,153 @@
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G119" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="22" customHeight="1">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B119" s="4" t="inlineStr">
+      <c r="B120" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C119" s="4" t="inlineStr">
+      <c r="C120" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D119" s="4" t="inlineStr">
+      <c r="D120" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
+      <c r="E120" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F119" s="4" t="inlineStr">
+      <c r="F120" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G119" s="6" t="inlineStr">
+      <c r="G120" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G119"/>
+  <autoFilter ref="A4:G120"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$121</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-13 07:20:28</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-14 05:47:17</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>14830</t>
+          <t>12804</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -4022,698 +4022,698 @@
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>292.70</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>290.90</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>296.50</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>290.30</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G99" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>12804</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>+0.72%</t>
         </is>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G102" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G103" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G104" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G105" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G106" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G107" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G108" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G113" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G115" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
@@ -4725,116 +4725,153 @@
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G119" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="22" customHeight="1">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B120" s="4" t="inlineStr">
+      <c r="B121" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C120" s="4" t="inlineStr">
+      <c r="C121" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D120" s="4" t="inlineStr">
+      <c r="D121" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
+      <c r="E121" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F120" s="4" t="inlineStr">
+      <c r="F121" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G120" s="6" t="inlineStr">
+      <c r="G121" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G120"/>
+  <autoFilter ref="A4:G121"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$122</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-14 05:47:17</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-15 05:32:26</t>
         </is>
       </c>
     </row>
@@ -3255,17 +3255,17 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>308.50</t>
+          <t>308.5</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>308.50</t>
+          <t>308.5</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>305.00</t>
+          <t>305.0</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -3310,9 +3310,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="G79" s="6" t="inlineStr">
-        <is>
-          <t>-2.51%</t>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>12804</t>
+          <t>16262</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
@@ -4059,698 +4059,698 @@
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>298.05</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>292.60</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>303.35</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>292.60</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>16262</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>+1.83%</t>
         </is>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G103" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G104" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G105" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G107" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G114" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G115" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr">
@@ -4762,116 +4762,153 @@
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G119" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G121" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="22" customHeight="1">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B121" s="4" t="inlineStr">
+      <c r="B122" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C121" s="4" t="inlineStr">
+      <c r="C122" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D121" s="4" t="inlineStr">
+      <c r="D122" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
+      <c r="E122" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F121" s="4" t="inlineStr">
+      <c r="F122" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G121" s="6" t="inlineStr">
+      <c r="G122" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G121"/>
+  <autoFilter ref="A4:G122"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-15 05:32:26</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-16 05:25:35</t>
         </is>
       </c>
     </row>
@@ -3347,9 +3347,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>-1.27%</t>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$124</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-16 05:25:35</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-17 05:18:26</t>
         </is>
       </c>
     </row>
@@ -3384,9 +3384,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="G81" s="6" t="inlineStr">
-        <is>
-          <t>-1.79%</t>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>12465</t>
+          <t>18321</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>15448</t>
+          <t>20967</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>16262</t>
+          <t>12804</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>16262</t>
+          <t>15825</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -4096,234 +4096,234 @@
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>294.80</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>296.65</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>298.85</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>291.95</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>13054</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-1.09%</t>
         </is>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>305.60</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>299.25</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>311.30</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>298.35</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="inlineStr">
-        <is>
-          <t>-2.19%</t>
+          <t>13054</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>+3.66%</t>
         </is>
       </c>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G104" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>15.13K</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
+          <t>13.83K</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
+          <t>12.68K</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -4333,582 +4333,656 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
+          <t>8.18K</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
+          <t>11.87K</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>+1.63%</t>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
+          <t>10.80K</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>-3.15%</t>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
+          <t>13.92K</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>+1.54%</t>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
-        </is>
-      </c>
-      <c r="G111" s="5" t="inlineStr">
-        <is>
-          <t>+2.31%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G115" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>23.18K</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
-        </is>
-      </c>
-      <c r="G116" s="6" t="inlineStr">
-        <is>
-          <t>-1.88%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G117" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G119" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G121" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="4" t="inlineStr">
         <is>
+          <t>2026年6月5日</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>246.5</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>248.0</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>249.2</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>243.3</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>26.62K</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr">
+        <is>
+          <t>-0.26%</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="22" customHeight="1">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G123" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="22" customHeight="1">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B122" s="4" t="inlineStr">
+      <c r="B124" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C122" s="4" t="inlineStr">
+      <c r="C124" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D122" s="4" t="inlineStr">
+      <c r="D124" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
+      <c r="E124" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F122" s="4" t="inlineStr">
+      <c r="F124" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G122" s="6" t="inlineStr">
+      <c r="G124" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G122"/>
+  <autoFilter ref="A4:G124"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-17 05:18:26</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-18 05:24:36</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>+1.38%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>305.60</t>
+          <t>305.55</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>311.30</t>
+          <t>311.20</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>13054</t>
+          <t>25328</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>+3.66%</t>
+          <t>+3.65%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-18 05:24:36</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-19 05:42:36</t>
         </is>
       </c>
     </row>
@@ -3458,9 +3458,9 @@
           <t>13363</t>
         </is>
       </c>
-      <c r="G83" s="6" t="inlineStr">
-        <is>
-          <t>-6.16%</t>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>305.55</t>
+          <t>305.60</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>311.20</t>
+          <t>311.30</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>25328</t>
+          <t>13054</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>+3.65%</t>
+          <t>+3.66%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$125</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-19 05:42:36</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-20 05:39:23</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>18321</t>
+          <t>12465</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>20967</t>
+          <t>15448</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>12804</t>
+          <t>16262</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>15825</t>
+          <t>16262</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>13054</t>
+          <t>25328</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -4170,698 +4170,698 @@
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>315.70</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>303.00</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>317.75</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>303.00</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G103" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>25328</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>+3.30%</t>
         </is>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G106" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G107" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G108" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G109" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G110" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G111" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G112" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G117" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G119" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G121" s="6" t="inlineStr">
@@ -4873,116 +4873,153 @@
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G123" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="22" customHeight="1">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B124" s="4" t="inlineStr">
+      <c r="B125" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C124" s="4" t="inlineStr">
+      <c r="C125" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D124" s="4" t="inlineStr">
+      <c r="D125" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
+      <c r="E125" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F124" s="4" t="inlineStr">
+      <c r="F125" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G124" s="6" t="inlineStr">
+      <c r="G125" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G124"/>
+  <autoFilter ref="A4:G125"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$126</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-20 05:39:23</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-21 05:42:03</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>25328</t>
+          <t>20781</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
@@ -4207,698 +4207,698 @@
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>311.30</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>315.00</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>318.20</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>309.20</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>20781</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-1.39%</t>
         </is>
       </c>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G107" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G110" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G111" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G112" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G113" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G118" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G119" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G121" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
@@ -4910,116 +4910,153 @@
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G123" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G125" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="22" customHeight="1">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B125" s="4" t="inlineStr">
+      <c r="B126" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C125" s="4" t="inlineStr">
+      <c r="C126" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D125" s="4" t="inlineStr">
+      <c r="D126" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr">
+      <c r="E126" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F125" s="4" t="inlineStr">
+      <c r="F126" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G125" s="6" t="inlineStr">
+      <c r="G126" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G125"/>
+  <autoFilter ref="A4:G126"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-21 05:42:03</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-22 05:44:35</t>
         </is>
       </c>
     </row>
@@ -3435,17 +3435,17 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>276.40</t>
+          <t>276.4</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>279.70</t>
+          <t>279.7</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>283.50</t>
+          <t>283.5</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -3495,9 +3495,9 @@
           <t>15733</t>
         </is>
       </c>
-      <c r="G84" s="6" t="inlineStr">
-        <is>
-          <t>-1.48%</t>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>20781</t>
+          <t>17372</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
@@ -4244,698 +4244,698 @@
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>316.15</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>311.30</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>317.90</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>308.35</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G105" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>17372</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>+1.56%</t>
         </is>
       </c>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G108" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G109" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G110" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G111" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G112" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G113" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G114" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G119" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G120" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G121" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G123" s="6" t="inlineStr">
@@ -4947,116 +4947,153 @@
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="22" customHeight="1">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B126" s="4" t="inlineStr">
+      <c r="B127" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C126" s="4" t="inlineStr">
+      <c r="C127" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D126" s="4" t="inlineStr">
+      <c r="D127" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
+      <c r="E127" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F126" s="4" t="inlineStr">
+      <c r="F127" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G126" s="6" t="inlineStr">
+      <c r="G127" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G126"/>
+  <autoFilter ref="A4:G127"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$128</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-22 05:44:35</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-23 05:43:08</t>
         </is>
       </c>
     </row>
@@ -3472,22 +3472,22 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>272.30</t>
+          <t>272.3</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>275.00</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>278.50</t>
+          <t>278.5</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>271.30</t>
+          <t>271.3</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>+1.32%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>12465</t>
+          <t>18321</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>15448</t>
+          <t>20967</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>16262</t>
+          <t>12804</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>16262</t>
+          <t>15825</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>17372</t>
+          <t>19611</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
@@ -4281,698 +4281,698 @@
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>312.45</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>315.40</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>315.50</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>302.25</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>19611</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-1.17%</t>
         </is>
       </c>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G110" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G111" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G112" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G113" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G114" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G115" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G120" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G121" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G123" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
@@ -4984,116 +4984,153 @@
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G127" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="22" customHeight="1">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B127" s="4" t="inlineStr">
+      <c r="B128" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C127" s="4" t="inlineStr">
+      <c r="C128" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D127" s="4" t="inlineStr">
+      <c r="D128" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
+      <c r="E128" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F127" s="4" t="inlineStr">
+      <c r="F128" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G127" s="6" t="inlineStr">
+      <c r="G128" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G127"/>
+  <autoFilter ref="A4:G128"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$129</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-23 05:43:08</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-24 05:22:17</t>
         </is>
       </c>
     </row>
@@ -3509,12 +3509,12 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>275.90</t>
+          <t>275.9</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>272.10</t>
+          <t>272.1</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -3569,9 +3569,9 @@
           <t>9519</t>
         </is>
       </c>
-      <c r="G86" s="6" t="inlineStr">
-        <is>
-          <t>-0.20%</t>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>18321</t>
+          <t>12465</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>12804</t>
+          <t>16262</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>15825</t>
+          <t>16262</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>19611</t>
+          <t>21092</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
@@ -4318,698 +4318,698 @@
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>307.45</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>310.05</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>314.90</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>305.30</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>21092</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-1.60%</t>
         </is>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G110" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G111" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G112" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G113" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G114" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G115" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G116" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G121" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G122" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G123" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G125" s="6" t="inlineStr">
@@ -5021,116 +5021,153 @@
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G127" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="22" customHeight="1">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B128" s="4" t="inlineStr">
+      <c r="B129" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C128" s="4" t="inlineStr">
+      <c r="C129" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D128" s="4" t="inlineStr">
+      <c r="D129" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
+      <c r="E129" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F128" s="4" t="inlineStr">
+      <c r="F129" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G128" s="6" t="inlineStr">
+      <c r="G129" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G128"/>
+  <autoFilter ref="A4:G129"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-24 05:22:17</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-25 05:39:39</t>
         </is>
       </c>
     </row>
@@ -3556,12 +3556,12 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>279.10</t>
+          <t>279.1</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>272.00</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>+1.18%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>307.45</t>
+          <t>306.00</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>310.05</t>
+          <t>315.40</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -4343,12 +4343,12 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>21092</t>
+          <t>14552</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>-1.60%</t>
+          <t>-2.06%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-25 05:39:39</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-26 05:45:30</t>
         </is>
       </c>
     </row>
@@ -3583,17 +3583,17 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>278.60</t>
+          <t>278.6</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>274.30</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>284.30</t>
+          <t>284.3</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>+3.64%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>306.00</t>
+          <t>307.45</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>315.40</t>
+          <t>310.05</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -4343,12 +4343,12 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>14552</t>
+          <t>21092</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>-2.06%</t>
+          <t>-1.60%</t>
         </is>
       </c>
     </row>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$130</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-26 05:45:30</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-27 05:58:13</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>12465</t>
+          <t>18321</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>16262</t>
+          <t>15825</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>21092</t>
+          <t>14552</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
@@ -4355,698 +4355,698 @@
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>300.95</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>298.40</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>304.00</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>294.90</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>14552</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-2.11%</t>
         </is>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G111" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G112" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G113" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G114" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G115" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G116" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G117" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G117" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G122" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G123" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
@@ -5058,116 +5058,153 @@
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G127" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G129" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="22" customHeight="1">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B129" s="4" t="inlineStr">
+      <c r="B130" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C129" s="4" t="inlineStr">
+      <c r="C130" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D129" s="4" t="inlineStr">
+      <c r="D130" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
+      <c r="E130" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F129" s="4" t="inlineStr">
+      <c r="F130" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G129" s="6" t="inlineStr">
+      <c r="G130" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G129"/>
+  <autoFilter ref="A4:G130"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$131</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G130"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-27 05:58:13</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-28 06:36:32</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>14552</t>
+          <t>20571</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
@@ -4392,698 +4392,698 @@
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>293.75</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>303.00</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>304.90</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>289.05</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>20571</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-2.39%</t>
         </is>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G112" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G113" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G114" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G115" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G116" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G117" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G118" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G123" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G124" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G127" s="6" t="inlineStr">
@@ -5095,116 +5095,153 @@
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G129" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="22" customHeight="1">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B130" s="4" t="inlineStr">
+      <c r="B131" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C130" s="4" t="inlineStr">
+      <c r="C131" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D130" s="4" t="inlineStr">
+      <c r="D131" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
+      <c r="E131" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F130" s="4" t="inlineStr">
+      <c r="F131" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G130" s="6" t="inlineStr">
+      <c r="G131" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G130"/>
+  <autoFilter ref="A4:G131"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$132</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-28 06:36:32</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-29 06:44:34</t>
         </is>
       </c>
     </row>
@@ -3625,12 +3625,12 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>277.90</t>
+          <t>277.9</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>291.50</t>
+          <t>291.5</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>20571</t>
+          <t>18132</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
@@ -4429,698 +4429,698 @@
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>286.75</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>292.95</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>293.15</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>284.05</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>18132</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-2.38%</t>
         </is>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G113" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G114" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G115" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G116" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G117" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G117" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G118" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G119" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G119" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G124" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G125" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G127" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
@@ -5132,116 +5132,153 @@
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G129" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G131" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="22" customHeight="1">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B131" s="4" t="inlineStr">
+      <c r="B132" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C131" s="4" t="inlineStr">
+      <c r="C132" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D131" s="4" t="inlineStr">
+      <c r="D132" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
+      <c r="E132" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F131" s="4" t="inlineStr">
+      <c r="F132" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G131" s="6" t="inlineStr">
+      <c r="G132" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G131"/>
+  <autoFilter ref="A4:G132"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$133</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G132"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-29 06:44:34</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-30 06:46:52</t>
         </is>
       </c>
     </row>
@@ -3662,17 +3662,17 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>289.00</t>
+          <t>289.0</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>293.40</t>
+          <t>293.4</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>281.80</t>
+          <t>281.8</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+0.00%</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>18132</t>
+          <t>18365</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
@@ -4466,698 +4466,698 @@
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>285.45</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>287.15</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>288.65</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>280.80</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
+          <t>18365</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-0.45%</t>
         </is>
       </c>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G114" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G115" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G116" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G117" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G118" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G119" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G120" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G125" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G126" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G127" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G129" s="6" t="inlineStr">
@@ -5169,116 +5169,153 @@
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G131" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="22" customHeight="1">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B132" s="4" t="inlineStr">
+      <c r="B133" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C132" s="4" t="inlineStr">
+      <c r="C133" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D132" s="4" t="inlineStr">
+      <c r="D133" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
+      <c r="E133" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F132" s="4" t="inlineStr">
+      <c r="F133" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G132" s="6" t="inlineStr">
+      <c r="G133" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G132"/>
+  <autoFilter ref="A4:G133"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/coffee_price_history.xlsx
+++ b/coffee_price_history.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="咖啡期货历史数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'咖啡期货历史数据'!$A$4:$G$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-30 06:46:52</t>
+          <t>数据来源: Yahoo Finance (KC=F)  |  抓取时间: 2026-10-31 06:36:22</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>18365</t>
+          <t>18561</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
@@ -4503,698 +4503,698 @@
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>2026年5月18日</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>276.2</t>
+          <t>287.20</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>288.00</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>291.50</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>279.15</t>
+          <t>283.30</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>0.00K</t>
-        </is>
-      </c>
-      <c r="G112" s="6" t="inlineStr">
-        <is>
-          <t>-2.95%</t>
+          <t>18561</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>2026年5月19日</t>
+          <t>2026年5月18日</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>270.15</t>
+          <t>276.2</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>266.4</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>262.85</t>
+          <t>279.15</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>15.13K</t>
+          <t>0.00K</t>
         </is>
       </c>
       <c r="G113" s="6" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-2.95%</t>
         </is>
       </c>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>2026年5月20日</t>
+          <t>2026年5月19日</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>268.3</t>
+          <t>270.15</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
+          <t>266.4</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>272.0</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>264.2</t>
+          <t>262.85</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>13.83K</t>
+          <t>15.13K</t>
         </is>
       </c>
       <c r="G114" s="6" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-2.19%</t>
         </is>
       </c>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>2026年5月21日</t>
+          <t>2026年5月20日</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>268.3</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>274.3</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>264.2</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>12.68K</t>
-        </is>
-      </c>
-      <c r="G115" s="5" t="inlineStr">
-        <is>
-          <t>+1.90%</t>
+          <t>13.83K</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>-0.68%</t>
         </is>
       </c>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>2026年5月22日</t>
+          <t>2026年5月21日</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>272.35</t>
+          <t>273.4</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>274.8</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>270.7</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>8.18K</t>
-        </is>
-      </c>
-      <c r="G116" s="6" t="inlineStr">
-        <is>
-          <t>-0.38%</t>
+          <t>12.68K</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>+1.90%</t>
         </is>
       </c>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>2026年5月26日</t>
+          <t>2026年5月22日</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>274.0</t>
+          <t>272.35</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>270.4</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>274.8</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>267.15</t>
+          <t>270.7</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>11.87K</t>
-        </is>
-      </c>
-      <c r="G117" s="5" t="inlineStr">
-        <is>
-          <t>+0.61%</t>
+          <t>8.18K</t>
+        </is>
+      </c>
+      <c r="G117" s="6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
         </is>
       </c>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>2026年5月27日</t>
+          <t>2026年5月26日</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>269.85</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>273.85</t>
+          <t>270.4</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>276.8</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>268.8</t>
+          <t>267.15</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>10.80K</t>
-        </is>
-      </c>
-      <c r="G118" s="6" t="inlineStr">
-        <is>
-          <t>-1.51%</t>
+          <t>11.87K</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
         </is>
       </c>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>2026年5月28日</t>
+          <t>2026年5月27日</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>274.25</t>
+          <t>269.85</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>271.0</t>
+          <t>273.85</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>278.4</t>
+          <t>276.8</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>270.95</t>
+          <t>268.8</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>13.92K</t>
-        </is>
-      </c>
-      <c r="G119" s="5" t="inlineStr">
-        <is>
-          <t>+1.63%</t>
+          <t>10.80K</t>
+        </is>
+      </c>
+      <c r="G119" s="6" t="inlineStr">
+        <is>
+          <t>-1.51%</t>
         </is>
       </c>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>2026年5月29日</t>
+          <t>2026年5月28日</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>274.25</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>273.25</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>274.6</t>
+          <t>278.4</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>265.3</t>
+          <t>270.95</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>14.22K</t>
-        </is>
-      </c>
-      <c r="G120" s="6" t="inlineStr">
-        <is>
-          <t>-3.15%</t>
+          <t>13.92K</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>+1.63%</t>
         </is>
       </c>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>2026年6月10日</t>
+          <t>2026年5月29日</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>244.6</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>241.55</t>
+          <t>273.25</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>246.0</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>265.3</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>26.81K</t>
-        </is>
-      </c>
-      <c r="G121" s="5" t="inlineStr">
-        <is>
-          <t>+1.54%</t>
+          <t>14.22K</t>
+        </is>
+      </c>
+      <c r="G121" s="6" t="inlineStr">
+        <is>
+          <t>-3.15%</t>
         </is>
       </c>
     </row>
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>2026年6月11日</t>
+          <t>2026年6月10日</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>250.25</t>
+          <t>244.6</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>243.65</t>
+          <t>241.55</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>251.7</t>
+          <t>246.0</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>243.6</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>25.64K</t>
+          <t>26.81K</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>+2.31%</t>
+          <t>+1.54%</t>
         </is>
       </c>
     </row>
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>2026年6月12日</t>
+          <t>2026年6月11日</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>253.4</t>
+          <t>250.25</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>251.15</t>
+          <t>243.65</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>254.35</t>
+          <t>251.7</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>249.25</t>
+          <t>243.6</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>21.91K</t>
+          <t>25.64K</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+2.31%</t>
         </is>
       </c>
     </row>
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>2026年6月15日</t>
+          <t>2026年6月12日</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>253.4</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>251.15</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>254.35</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>252.25</t>
+          <t>249.25</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>23.18K</t>
+          <t>21.91K</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+1.26%</t>
         </is>
       </c>
     </row>
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>2026年6月16日</t>
+          <t>2026年6月15日</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>272.8</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>259.6</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>274.95</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>256.4</t>
+          <t>252.25</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>30.91K</t>
+          <t>23.18K</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>+5.25%</t>
+          <t>+2.29%</t>
         </is>
       </c>
     </row>
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>2026年6月17日</t>
+          <t>2026年6月16日</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>271.9</t>
+          <t>272.8</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>273.0</t>
+          <t>259.6</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>274.7</t>
+          <t>274.95</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>266.45</t>
+          <t>256.4</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>26.40K</t>
-        </is>
-      </c>
-      <c r="G126" s="6" t="inlineStr">
-        <is>
-          <t>-0.33%</t>
+          <t>30.91K</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>+5.25%</t>
         </is>
       </c>
     </row>
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>2026年6月1日</t>
+          <t>2026年6月17日</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>260.6</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>265.85</t>
+          <t>273.0</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>269.4</t>
+          <t>274.7</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>259.55</t>
+          <t>266.45</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>17.19K</t>
+          <t>26.40K</t>
         </is>
       </c>
       <c r="G127" s="6" t="inlineStr">
         <is>
-          <t>-1.88%</t>
+          <t>-0.33%</t>
         </is>
       </c>
     </row>
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>2026年6月2日</t>
+          <t>2026年6月1日</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>259.2</t>
+          <t>260.6</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>260.7</t>
+          <t>265.85</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>262.3</t>
+          <t>269.4</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>258.15</t>
+          <t>259.55</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>12.71K</t>
+          <t>17.19K</t>
         </is>
       </c>
       <c r="G128" s="6" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.88%</t>
         </is>
       </c>
     </row>
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>2026年6月3日</t>
+          <t>2026年6月2日</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>253.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>261.1</t>
+          <t>260.7</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>261.7</t>
+          <t>262.3</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>252.4</t>
+          <t>258.15</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>19.79K</t>
+          <t>12.71K</t>
         </is>
       </c>
       <c r="G129" s="6" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>2026年6月4日</t>
+          <t>2026年6月3日</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>247.15</t>
+          <t>253.1</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>252.75</t>
+          <t>261.1</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>254.1</t>
+          <t>261.7</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>246.85</t>
+          <t>252.4</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>19.03K</t>
+          <t>19.79K</t>
         </is>
       </c>
       <c r="G130" s="6" t="inlineStr">
@@ -5206,116 +5206,153 @@
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>2026年6月5日</t>
+          <t>2026年6月4日</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>246.5</t>
+          <t>247.15</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>252.75</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>249.2</t>
+          <t>254.1</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>243.3</t>
+          <t>246.85</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>26.62K</t>
+          <t>19.03K</t>
         </is>
       </c>
       <c r="G131" s="6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-2.35%</t>
         </is>
       </c>
     </row>
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>2026年6月8日</t>
+          <t>2026年6月5日</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>241.65</t>
+          <t>246.5</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>246.1</t>
+          <t>249.2</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>243.3</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>19.98K</t>
+          <t>26.62K</t>
         </is>
       </c>
       <c r="G132" s="6" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
     <row r="133" ht="22" customHeight="1">
       <c r="A133" s="4" t="inlineStr">
         <is>
+          <t>2026年6月8日</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>241.65</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>242.0</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>240.0</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>19.98K</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr">
+        <is>
+          <t>-1.97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="22" customHeight="1">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
           <t>2026年6月9日</t>
         </is>
       </c>
-      <c r="B133" s="4" t="inlineStr">
+      <c r="B134" s="4" t="inlineStr">
         <is>
           <t>240.9</t>
         </is>
       </c>
-      <c r="C133" s="4" t="inlineStr">
+      <c r="C134" s="4" t="inlineStr">
         <is>
           <t>241.65</t>
         </is>
       </c>
-      <c r="D133" s="4" t="inlineStr">
+      <c r="D134" s="4" t="inlineStr">
         <is>
           <t>244.65</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
+      <c r="E134" s="4" t="inlineStr">
         <is>
           <t>238.85</t>
         </is>
       </c>
-      <c r="F133" s="4" t="inlineStr">
+      <c r="F134" s="4" t="inlineStr">
         <is>
           <t>26.41K</t>
         </is>
       </c>
-      <c r="G133" s="6" t="inlineStr">
+      <c r="G134" s="6" t="inlineStr">
         <is>
           <t>-0.31%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G133"/>
+  <autoFilter ref="A4:G134"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
